--- a/2022 data/excel_outputs/160_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/160_boothwise_data.xlsx
@@ -14,11 +14,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="482">
   <si>
     <t>AC 160 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -520,7 +583,7 @@
     <t>P. P. ARSENI MAJRA TIKARI ROOM NO-1</t>
   </si>
   <si>
-    <t>P. P. ARSENI MAJRA TIKARI ROOM NO-■</t>
+    <t>P. P. KATKA</t>
   </si>
   <si>
     <t>P. P. TUSAURA MAJRA TIKARI ROOM NO-1</t>
@@ -595,9 +658,6 @@
     <t>P. P. MAHMADPUR MAJRA MAHRI</t>
   </si>
   <si>
-    <t>P. P. KATKA</t>
-  </si>
-  <si>
     <t>P. P. BARRAGHAGUMAN</t>
   </si>
   <si>
@@ -649,7 +709,7 @@
     <t>P. P. KUKUHI ROOM NO-1</t>
   </si>
   <si>
-    <t>P. P. KUKUHI ROOM NO-■</t>
+    <t>J. H. SCHOOL RAISO ROOM NO.1</t>
   </si>
   <si>
     <t>P. P. KUKUHI ROOM NO-3</t>
@@ -1406,8 +1466,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1423,7 +1491,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1431,12 +1499,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1735,76 +1821,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="F2" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="G2" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H2" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="I2" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="J2" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="K2" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="L2" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="M2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="N2" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="O2" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="P2" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="Q2" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="R2" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="S2" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="T2" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="U2" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="V2" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1812,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1880,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1948,7 +2097,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2016,7 +2165,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2084,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2152,7 +2301,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2220,7 +2369,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2288,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2356,7 +2505,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2424,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2492,7 +2641,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2560,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2628,7 +2777,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2696,7 +2845,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2764,7 +2913,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2832,7 +2981,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2900,7 +3049,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2968,7 +3117,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3036,7 +3185,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3104,7 +3253,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3172,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3240,7 +3389,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3308,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3376,7 +3525,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3444,7 +3593,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3512,7 +3661,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3580,7 +3729,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3648,7 +3797,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3716,7 +3865,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3784,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3852,7 +4001,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3920,7 +4069,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -3988,7 +4137,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4056,7 +4205,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4124,7 +4273,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4192,7 +4341,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4260,7 +4409,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4328,7 +4477,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4396,7 +4545,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4464,7 +4613,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4532,7 +4681,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4600,7 +4749,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4668,7 +4817,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4736,7 +4885,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -4804,7 +4953,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4872,7 +5021,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4940,7 +5089,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5008,7 +5157,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5076,7 +5225,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5144,7 +5293,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5212,7 +5361,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5280,7 +5429,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5348,7 +5497,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5416,7 +5565,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5484,7 +5633,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5552,7 +5701,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -5620,7 +5769,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -5688,7 +5837,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5756,7 +5905,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -5824,7 +5973,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -5892,7 +6041,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5960,7 +6109,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6028,7 +6177,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6096,7 +6245,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6164,7 +6313,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6232,7 +6381,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6300,7 +6449,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6368,7 +6517,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -6436,7 +6585,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -6504,7 +6653,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -6572,7 +6721,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6640,7 +6789,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6708,7 +6857,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6776,7 +6925,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -6844,7 +6993,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -6912,7 +7061,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -6980,7 +7129,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7048,7 +7197,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7116,7 +7265,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7184,7 +7333,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -7252,7 +7401,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -7320,7 +7469,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -7388,7 +7537,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -7456,7 +7605,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -7524,7 +7673,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -7592,7 +7741,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -7660,7 +7809,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7728,7 +7877,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -7796,7 +7945,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -7864,7 +8013,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -7932,7 +8081,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8000,7 +8149,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8068,7 +8217,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -8136,7 +8285,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -8204,7 +8353,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -8272,7 +8421,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -8340,7 +8489,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -8408,7 +8557,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -8476,7 +8625,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -8544,7 +8693,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -8612,7 +8761,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -8680,7 +8829,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -8748,7 +8897,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -8816,7 +8965,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -8884,7 +9033,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -8952,7 +9101,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -9020,7 +9169,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -9088,7 +9237,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -9156,7 +9305,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -9224,7 +9373,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -9292,7 +9441,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -9360,7 +9509,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -9428,7 +9577,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -9496,7 +9645,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -9564,7 +9713,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -9632,7 +9781,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -9700,7 +9849,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -9768,7 +9917,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -9836,7 +9985,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -9904,7 +10053,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -9972,7 +10121,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -10040,7 +10189,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -10108,7 +10257,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -10176,7 +10325,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -10244,7 +10393,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -10312,7 +10461,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -10380,7 +10529,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -10448,7 +10597,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -10516,7 +10665,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -10584,7 +10733,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -10652,7 +10801,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -10720,7 +10869,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -10788,7 +10937,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -10856,7 +11005,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -10924,7 +11073,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -10992,7 +11141,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -11060,7 +11209,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -11128,7 +11277,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -11196,7 +11345,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -11264,7 +11413,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -11332,7 +11481,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -11400,7 +11549,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -11468,7 +11617,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -11536,7 +11685,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -11604,7 +11753,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -11672,7 +11821,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -11740,7 +11889,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -11808,7 +11957,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -11876,7 +12025,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -11944,7 +12093,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12012,7 +12161,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12080,7 +12229,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12148,7 +12297,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12216,7 +12365,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12284,7 +12433,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12352,7 +12501,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12420,7 +12569,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12488,7 +12637,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12556,7 +12705,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12624,7 +12773,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12692,7 +12841,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12760,7 +12909,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12828,7 +12977,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12896,7 +13045,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -12964,7 +13113,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -13032,7 +13181,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -13100,7 +13249,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -13168,7 +13317,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -13236,7 +13385,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -13304,7 +13453,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -13372,7 +13521,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -13440,7 +13589,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -13508,7 +13657,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -13576,7 +13725,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -13644,7 +13793,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -13712,7 +13861,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -13780,7 +13929,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -13848,7 +13997,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -13916,7 +14065,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -13984,7 +14133,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -14052,7 +14201,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -14120,7 +14269,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -14188,7 +14337,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -14256,7 +14405,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -14324,7 +14473,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -14392,7 +14541,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -14460,7 +14609,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -14528,7 +14677,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -14596,7 +14745,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -14664,7 +14813,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -14732,7 +14881,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -14800,7 +14949,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -14868,7 +15017,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -14936,7 +15085,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -15004,7 +15153,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -15072,7 +15221,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -15140,7 +15289,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -15208,7 +15357,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -15276,7 +15425,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -15344,7 +15493,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -15412,7 +15561,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -15480,7 +15629,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -15548,7 +15697,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -15616,7 +15765,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -15684,7 +15833,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -15752,7 +15901,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -15820,7 +15969,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -15888,7 +16037,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -15956,7 +16105,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -16024,7 +16173,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -16092,7 +16241,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -16160,7 +16309,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -16228,7 +16377,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -16296,7 +16445,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -16364,7 +16513,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -16432,7 +16581,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -16500,7 +16649,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -16568,7 +16717,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -16636,7 +16785,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -16704,7 +16853,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -16772,7 +16921,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -16840,7 +16989,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -16908,7 +17057,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -16976,7 +17125,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -17044,7 +17193,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -17112,7 +17261,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -17180,7 +17329,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -17248,7 +17397,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -17316,7 +17465,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -17384,7 +17533,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -17452,7 +17601,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -17520,7 +17669,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -17588,7 +17737,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -17656,7 +17805,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -17724,7 +17873,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -17792,7 +17941,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -17860,7 +18009,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -17928,7 +18077,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -17996,7 +18145,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -18064,7 +18213,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -18132,7 +18281,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -18200,7 +18349,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -18268,7 +18417,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -18336,7 +18485,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -18404,7 +18553,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -18472,7 +18621,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -18540,7 +18689,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -18608,7 +18757,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -18676,7 +18825,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -18744,7 +18893,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -18812,7 +18961,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -18880,7 +19029,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -18948,7 +19097,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -19016,7 +19165,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -19084,7 +19233,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -19152,7 +19301,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -19220,7 +19369,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -19288,7 +19437,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -19356,7 +19505,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -19424,7 +19573,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -19492,7 +19641,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -19560,7 +19709,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -19628,7 +19777,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -19696,7 +19845,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -19764,7 +19913,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -19832,7 +19981,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -19900,7 +20049,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -19968,7 +20117,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -20036,7 +20185,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -20104,7 +20253,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -20172,7 +20321,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -20240,7 +20389,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -20308,7 +20457,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -20376,7 +20525,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -20444,7 +20593,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -20512,7 +20661,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -20580,7 +20729,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -20648,7 +20797,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -20716,7 +20865,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -20784,7 +20933,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -20852,7 +21001,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -20920,7 +21069,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -20988,7 +21137,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -21056,7 +21205,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -21124,7 +21273,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -21192,7 +21341,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -21260,7 +21409,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -21328,7 +21477,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -21396,7 +21545,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -21464,7 +21613,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -21532,7 +21681,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -21600,7 +21749,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -21668,7 +21817,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -21736,7 +21885,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -21804,7 +21953,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -21872,7 +22021,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -21940,7 +22089,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -22008,7 +22157,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -22076,7 +22225,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -22144,7 +22293,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -22212,7 +22361,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -22280,7 +22429,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -22348,7 +22497,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -22416,7 +22565,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -22484,7 +22633,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -22552,7 +22701,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -22620,7 +22769,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -22688,7 +22837,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -22756,7 +22905,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -22824,7 +22973,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -22892,7 +23041,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -22960,7 +23109,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -23028,7 +23177,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -23096,7 +23245,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -23164,7 +23313,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -23232,7 +23381,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -23300,7 +23449,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -23368,7 +23517,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -23436,7 +23585,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -23504,7 +23653,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -23572,7 +23721,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -23640,7 +23789,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -23708,7 +23857,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -23776,7 +23925,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -23844,7 +23993,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -23912,7 +24061,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -23980,7 +24129,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -24048,7 +24197,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -24116,7 +24265,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -24184,7 +24333,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -24252,7 +24401,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -24320,7 +24469,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -24388,7 +24537,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -24456,7 +24605,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -24524,7 +24673,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -24592,7 +24741,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -24660,7 +24809,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -24728,7 +24877,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -24796,7 +24945,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -24864,7 +25013,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -24932,7 +25081,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -25000,7 +25149,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -25068,7 +25217,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -25136,7 +25285,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -25204,7 +25353,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -25272,7 +25421,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -25340,7 +25489,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -25408,7 +25557,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -25476,7 +25625,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -25544,7 +25693,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -25612,7 +25761,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -25680,7 +25829,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -25748,7 +25897,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -25816,7 +25965,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -25884,7 +26033,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -25952,7 +26101,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -26020,7 +26169,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -26088,7 +26237,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -26156,7 +26305,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -26224,7 +26373,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -26292,7 +26441,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -26360,7 +26509,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -26428,7 +26577,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -26496,7 +26645,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -26564,7 +26713,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -26632,7 +26781,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -26700,7 +26849,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -26768,7 +26917,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -26836,7 +26985,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -26904,7 +27053,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -26972,7 +27121,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -27040,7 +27189,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -27108,7 +27257,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -27176,7 +27325,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -27244,7 +27393,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -27312,7 +27461,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -27380,7 +27529,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -27448,7 +27597,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -27516,7 +27665,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -27584,7 +27733,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -27652,7 +27801,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -27720,7 +27869,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -27788,7 +27937,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -27856,7 +28005,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -27924,7 +28073,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -27992,7 +28141,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -28060,7 +28209,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -28128,7 +28277,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -28196,7 +28345,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -28264,7 +28413,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -28332,7 +28481,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -28400,7 +28549,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -28468,7 +28617,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -28536,7 +28685,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -28604,7 +28753,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -28672,7 +28821,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -28740,7 +28889,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -28808,7 +28957,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -28876,7 +29025,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -28944,7 +29093,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -29012,7 +29161,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -29080,7 +29229,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -29148,7 +29297,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -29216,7 +29365,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -29284,7 +29433,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -29352,7 +29501,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -29420,7 +29569,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -29488,7 +29637,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -29556,7 +29705,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -29624,7 +29773,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -29692,7 +29841,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C413">
         <v>0</v>
@@ -29760,7 +29909,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -29828,7 +29977,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="C415">
         <v>0</v>
@@ -29896,7 +30045,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="C416">
         <v>0</v>
@@ -29964,7 +30113,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -30032,7 +30181,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -30100,7 +30249,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -30168,7 +30317,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -30236,7 +30385,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -30304,7 +30453,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C422">
         <v>0</v>
@@ -30372,7 +30521,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="C423">
         <v>0</v>
@@ -30440,7 +30589,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="C424">
         <v>0</v>
@@ -30508,7 +30657,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -30576,7 +30725,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -30644,7 +30793,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -30712,7 +30861,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -30780,7 +30929,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="C429">
         <v>0</v>
@@ -30848,7 +30997,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C430">
         <v>0</v>
@@ -30916,7 +31065,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -30984,7 +31133,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C432">
         <v>0</v>
@@ -31052,7 +31201,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C433">
         <v>0</v>
@@ -31120,7 +31269,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -31188,7 +31337,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -31256,7 +31405,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -31324,7 +31473,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C437">
         <v>0</v>
@@ -31392,7 +31541,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -31460,7 +31609,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C439">
         <v>0</v>
@@ -31528,7 +31677,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C440">
         <v>0</v>
@@ -31596,7 +31745,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C441">
         <v>0</v>
